--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="177" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCE8A816-9E22-40AD-9769-9659CD9B07C7}"/>
+  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECBBAE6-2420-4947-B3B4-DB80101D855C}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
   <si>
     <t>Wk</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Testing first instance of gesture recognition app</t>
+  </si>
+  <si>
+    <t>Coded and registered gestures as vectors and gesture recognition core</t>
   </si>
 </sst>
 </file>
@@ -1566,21 +1569,35 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="G26" s="6" t="str">
+      <c r="A26" s="1">
+        <v>5</v>
+      </c>
+      <c r="B26" s="4">
+        <v>44787</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D26" s="4">
+        <v>44787</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0.625</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H26" s="1" t="str">
+        <v>2.0000000000582077</v>
+      </c>
+      <c r="H26" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>18.500000000058208</v>
       </c>
       <c r="I26" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.0000000000582077</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">

--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="183" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4ECBBAE6-2420-4947-B3B4-DB80101D855C}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A364A3B5-E424-42FD-95C7-AC5A11C039A6}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4476" yWindow="2424" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>Wk</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>Coded and registered gestures as vectors and gesture recognition core</t>
+  </si>
+  <si>
+    <t>Tested and debugged recognition app</t>
   </si>
 </sst>
 </file>
@@ -354,6 +357,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -372,14 +383,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -473,6 +476,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -813,36 +820,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
@@ -862,7 +869,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1601,21 +1608,35 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="G27" s="6" t="str">
+      <c r="A27" s="1">
+        <v>5</v>
+      </c>
+      <c r="B27" s="4">
+        <v>44789</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="4">
+        <v>44789</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H27" s="1" t="str">
+        <v>0.99999999994179234</v>
+      </c>
+      <c r="H27" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>19.5</v>
       </c>
       <c r="I27" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.99999999994179234</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1676,14 +1697,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2285,14 +2306,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2781,14 +2802,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3275,18 +3296,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3300,6 +3309,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A364A3B5-E424-42FD-95C7-AC5A11C039A6}"/>
+  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF789072-2CE2-4E9C-BDD1-FC04905784BC}"/>
   <bookViews>
     <workbookView xWindow="4476" yWindow="2424" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
   <si>
     <t>Wk</t>
   </si>
@@ -357,14 +357,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -383,6 +375,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -820,36 +820,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1640,39 +1640,67 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="G28" s="6" t="str">
+      <c r="A28" s="1">
+        <v>5</v>
+      </c>
+      <c r="B28" s="4">
+        <v>44791</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D28" s="4">
+        <v>44791</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0.53125</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H28" s="1" t="str">
+        <v>1.7499999999417923</v>
+      </c>
+      <c r="H28" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>21.249999999941792</v>
       </c>
       <c r="I28" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.7499999999417923</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="G29" s="6" t="str">
+      <c r="A29" s="1">
+        <v>5</v>
+      </c>
+      <c r="B29" s="4">
+        <v>44791</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D29" s="4">
+        <v>44791</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0.5625</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H29" s="1" t="str">
+        <v>0.50000000005820766</v>
+      </c>
+      <c r="H29" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>21.75</v>
       </c>
       <c r="I29" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.50000000005820766</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1697,14 +1725,14 @@
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -2306,14 +2334,14 @@
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2802,14 +2830,14 @@
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -3296,6 +3324,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3309,18 +3349,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="202" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF789072-2CE2-4E9C-BDD1-FC04905784BC}"/>
+  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE5FD11F-6F31-4CFB-A640-7CCA45347A1D}"/>
   <bookViews>
-    <workbookView xWindow="4476" yWindow="2424" windowWidth="17280" windowHeight="10008" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="27">
   <si>
     <t>Wk</t>
   </si>
@@ -126,6 +126,9 @@
   </si>
   <si>
     <t>Tested and debugged recognition app</t>
+  </si>
+  <si>
+    <t>Formal recognition app testing</t>
   </si>
 </sst>
 </file>
@@ -357,6 +360,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -375,14 +386,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -805,55 +808,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="52.453125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6328125" style="1"/>
-    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.6328125" style="1"/>
+    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="D2" s="15" t="s">
+      <c r="C2" s="11"/>
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="15" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -869,7 +872,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="14"/>
+      <c r="H3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1704,35 +1707,49 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
-      <c r="G30" s="6" t="str">
+      <c r="A30" s="1">
+        <v>5</v>
+      </c>
+      <c r="B30" s="4">
+        <v>44793</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="D30" s="4">
+        <v>44793</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6">
         <f t="shared" si="1"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="H30" s="1" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="H30" s="1">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
+        <v>23.25</v>
       </c>
       <c r="I30" s="1">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="B31" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="15" t="s">
+      <c r="C31" s="11"/>
+      <c r="D31" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="16"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1747,7 +1764,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2330,18 +2347,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="B65" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="16"/>
-      <c r="D65" s="15" t="s">
+      <c r="C65" s="11"/>
+      <c r="D65" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="16"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2356,7 +2373,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -2826,18 +2843,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="16"/>
-      <c r="D99" s="15" t="s">
+      <c r="C99" s="11"/>
+      <c r="D99" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="16"/>
+      <c r="E99" s="11"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2852,7 +2869,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3324,18 +3341,6 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3349,6 +3354,18 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3360,7 +3377,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3372,7 +3389,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
+++ b/Documentation/Week 5/Booked Hours/Booked_Hours_Christo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24432207_student_uwa_edu_au/Documents/UWA - Student/2026_Sem2/CITS3200 - Professional Computing/Project/Repo/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniwa-my.sharepoint.com/personal/24314441_student_uwa_edu_au/Documents/UWA/Year 3/Sem 2/CITS3200_Project/Documentation/Week 5/Booked Hours/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="213" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE5FD11F-6F31-4CFB-A640-7CCA45347A1D}"/>
+  <xr:revisionPtr revIDLastSave="215" documentId="13_ncr:40009_{31A31D98-CA30-574B-8C94-F50C456CB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F521061-531A-436F-A0CA-5FB3C9066B7A}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BookedHours" sheetId="1" r:id="rId1"/>
@@ -360,14 +360,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
@@ -386,6 +378,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -479,10 +479,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -808,55 +804,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I132"/>
-  <sheetFormatPr defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6328125" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="64.125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.625" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.625" style="1"/>
+    <col min="1" max="1" width="5.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="64.08984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.36328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6328125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6328125" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:9" ht="70.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="14"/>
-    </row>
-    <row r="2" spans="1:9" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="12"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="16"/>
+      <c r="D2" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="11"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="17" t="s">
         <v>5</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H2" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9"/>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -872,7 +868,7 @@
       </c>
       <c r="F3" s="18"/>
       <c r="G3" s="9"/>
-      <c r="H3" s="16"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1738,18 +1734,18 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="10" t="s">
+      <c r="C31" s="16"/>
+      <c r="D31" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E31" s="11"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="7" t="s">
         <v>5</v>
       </c>
@@ -1764,7 +1760,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="2" t="s">
         <v>2</v>
@@ -2347,18 +2343,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="11"/>
-      <c r="D65" s="10" t="s">
+      <c r="C65" s="16"/>
+      <c r="D65" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E65" s="11"/>
+      <c r="E65" s="16"/>
       <c r="F65" s="7" t="s">
         <v>5</v>
       </c>
@@ -2373,7 +2369,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A66" s="9"/>
       <c r="B66" s="2" t="s">
         <v>2</v>
@@ -2843,18 +2839,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="11"/>
-      <c r="D99" s="10" t="s">
+      <c r="C99" s="16"/>
+      <c r="D99" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E99" s="11"/>
+      <c r="E99" s="16"/>
       <c r="F99" s="7" t="s">
         <v>5</v>
       </c>
@@ -2869,7 +2865,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" ht="15" x14ac:dyDescent="0.25">
       <c r="A100" s="9"/>
       <c r="B100" s="2" t="s">
         <v>2</v>
@@ -3341,6 +3337,18 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="H99:H100"/>
+    <mergeCell ref="A99:A100"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="D99:E99"/>
+    <mergeCell ref="F99:F100"/>
+    <mergeCell ref="G99:G100"/>
+    <mergeCell ref="G65:G66"/>
+    <mergeCell ref="H65:H66"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="D65:E65"/>
+    <mergeCell ref="F65:F66"/>
     <mergeCell ref="H31:H32"/>
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="A1:H1"/>
@@ -3354,18 +3362,6 @@
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:F32"/>
     <mergeCell ref="G31:G32"/>
-    <mergeCell ref="G65:G66"/>
-    <mergeCell ref="H65:H66"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="D65:E65"/>
-    <mergeCell ref="F65:F66"/>
-    <mergeCell ref="H99:H100"/>
-    <mergeCell ref="A99:A100"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="D99:E99"/>
-    <mergeCell ref="F99:F100"/>
-    <mergeCell ref="G99:G100"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -3377,7 +3373,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3389,7 +3385,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
